--- a/activity/M01A05/M01A05_HECRASSample.xlsx
+++ b/activity/M01A05/M01A05_HECRASSample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07E1529-2A16-42DA-B402-AC113FFA9E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0EB9D4-CF79-4766-8B84-EBC166B2F7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="49">
   <si>
     <t>Observaciones</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Grupo 14</t>
   </si>
   <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A05/Readme.md</t>
-  </si>
-  <si>
     <t>Calificación: 1.5. Modelo topológico de muestreo en HEC-RAS para el estudio de secciones y perfiles</t>
   </si>
   <si>
@@ -259,12 +256,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -277,6 +268,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
@@ -615,31 +612,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -648,19 +645,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -669,11 +669,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1743,15 +1740,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>23530</xdr:colOff>
+      <xdr:colOff>14601</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>13435</xdr:rowOff>
+      <xdr:rowOff>16412</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>116155</xdr:colOff>
+      <xdr:colOff>107226</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>115198</xdr:rowOff>
+      <xdr:rowOff>118175</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2079,7 +2076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B1:F19"/>
+  <dimension ref="B1:F20"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="14" customWidth="1"/>
@@ -2095,12 +2092,12 @@
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="E1" s="24"/>
       <c r="F1" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="34"/>
       <c r="D2" s="34"/>
@@ -2370,26 +2367,32 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
+      <c r="B19" s="43" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A05 en GitHub.</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{2072EF7C-B410-484D-AB7A-7C0A233225B1}"/>
-  </hyperlinks>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2455,82 +2458,82 @@
     </row>
     <row r="2" spans="1:30" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="38" t="str">
+      <c r="C2" s="37" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="40" t="str">
+      <c r="D2" s="38"/>
+      <c r="E2" s="41" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="40" t="str">
+      <c r="F2" s="42"/>
+      <c r="G2" s="41" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="38" t="str">
+      <c r="H2" s="42"/>
+      <c r="I2" s="37" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="J2" s="39"/>
-      <c r="K2" s="38" t="str">
+      <c r="J2" s="38"/>
+      <c r="K2" s="37" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="L2" s="39"/>
-      <c r="M2" s="38" t="str">
+      <c r="L2" s="38"/>
+      <c r="M2" s="37" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="N2" s="39"/>
-      <c r="O2" s="38" t="str">
+      <c r="N2" s="38"/>
+      <c r="O2" s="37" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="38" t="str">
+      <c r="P2" s="38"/>
+      <c r="Q2" s="37" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="R2" s="39"/>
-      <c r="S2" s="38" t="str">
+      <c r="R2" s="38"/>
+      <c r="S2" s="37" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="T2" s="39"/>
-      <c r="U2" s="38" t="str">
+      <c r="T2" s="38"/>
+      <c r="U2" s="37" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="V2" s="39"/>
-      <c r="W2" s="38" t="str">
+      <c r="V2" s="38"/>
+      <c r="W2" s="37" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="38" t="str">
+      <c r="X2" s="38"/>
+      <c r="Y2" s="37" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="38" t="str">
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="37" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="38" t="str">
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="37" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AD2" s="39"/>
+      <c r="AD2" s="38"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B3" s="43"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -2618,7 +2621,7 @@
     </row>
     <row r="4" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="28">
         <v>0</v>
@@ -2844,7 +2847,7 @@
     </row>
     <row r="10" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="29"/>
@@ -2910,7 +2913,7 @@
     </row>
     <row r="12" spans="1:30" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="29"/>
@@ -3669,7 +3672,7 @@
     </row>
     <row r="35" spans="1:30" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B35" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="28"/>
       <c r="D35" s="29"/>
@@ -3702,7 +3705,7 @@
     </row>
     <row r="36" spans="1:30" ht="138.4" x14ac:dyDescent="0.45">
       <c r="B36" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" s="28"/>
       <c r="D36" s="29"/>
@@ -3735,7 +3738,7 @@
     </row>
     <row r="37" spans="1:30" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B37" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C37" s="28"/>
       <c r="D37" s="29"/>
@@ -3802,76 +3805,76 @@
       <c r="B39" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="39">
         <f>AVERAGE(C4:C38)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="36">
+      <c r="D39" s="40"/>
+      <c r="E39" s="39">
         <f>AVERAGE(E4:E38)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="37"/>
-      <c r="G39" s="36">
+      <c r="F39" s="40"/>
+      <c r="G39" s="39">
         <f>AVERAGE(G4:G38)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36">
+      <c r="H39" s="39"/>
+      <c r="I39" s="39">
         <f>AVERAGE(I4:I38)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="37"/>
-      <c r="K39" s="36">
+      <c r="J39" s="40"/>
+      <c r="K39" s="39">
         <f>AVERAGE(K4:K38)</f>
         <v>0</v>
       </c>
-      <c r="L39" s="37"/>
-      <c r="M39" s="36">
+      <c r="L39" s="40"/>
+      <c r="M39" s="39">
         <f>AVERAGE(M4:M38)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="37"/>
-      <c r="O39" s="36">
+      <c r="N39" s="40"/>
+      <c r="O39" s="39">
         <f>AVERAGE(O4:O38)</f>
         <v>0</v>
       </c>
-      <c r="P39" s="37"/>
-      <c r="Q39" s="36">
+      <c r="P39" s="40"/>
+      <c r="Q39" s="39">
         <f>AVERAGE(Q4:Q38)</f>
         <v>0</v>
       </c>
-      <c r="R39" s="37"/>
-      <c r="S39" s="36">
+      <c r="R39" s="40"/>
+      <c r="S39" s="39">
         <f>AVERAGE(S4:S38)</f>
         <v>0</v>
       </c>
-      <c r="T39" s="37"/>
-      <c r="U39" s="36">
+      <c r="T39" s="40"/>
+      <c r="U39" s="39">
         <f>AVERAGE(U4:U38)</f>
         <v>0</v>
       </c>
-      <c r="V39" s="37"/>
-      <c r="W39" s="36">
+      <c r="V39" s="40"/>
+      <c r="W39" s="39">
         <f>AVERAGE(W4:W38)</f>
         <v>0</v>
       </c>
-      <c r="X39" s="37"/>
-      <c r="Y39" s="36">
+      <c r="X39" s="40"/>
+      <c r="Y39" s="39">
         <f>AVERAGE(Y4:Y38)</f>
         <v>0</v>
       </c>
-      <c r="Z39" s="37"/>
-      <c r="AA39" s="36">
+      <c r="Z39" s="40"/>
+      <c r="AA39" s="39">
         <f>AVERAGE(AA4:AA38)</f>
         <v>0</v>
       </c>
-      <c r="AB39" s="37"/>
-      <c r="AC39" s="36">
+      <c r="AB39" s="40"/>
+      <c r="AC39" s="39">
         <f>AVERAGE(AC4:AC38)</f>
         <v>0</v>
       </c>
-      <c r="AD39" s="37"/>
+      <c r="AD39" s="40"/>
     </row>
     <row r="40" spans="1:30" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B40" s="3"/>
@@ -4991,6 +4994,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="AA39:AB39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="Y39:Z39"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AC2:AD2"/>
     <mergeCell ref="AC39:AD39"/>
@@ -5007,19 +5023,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="AA39:AB39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="Y39:Z39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A05/M01A05_HECRASSample.xlsx
+++ b/activity/M01A05/M01A05_HECRASSample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0EB9D4-CF79-4766-8B84-EBC166B2F7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF17143-EFCE-4144-9BCC-A4CBA0CB7AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -615,12 +615,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -644,6 +638,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -669,8 +666,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -787,8 +787,8 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="90000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -2096,20 +2096,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
@@ -2132,14 +2132,14 @@
       <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="42">
         <v>5</v>
       </c>
       <c r="D5" s="22">
         <f>C5*Detalle!C39/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="42"/>
       <c r="F5" s="16">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2149,14 +2149,14 @@
       <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="42">
         <v>5</v>
       </c>
       <c r="D6" s="22">
         <f>C6*Detalle!E39/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="42"/>
       <c r="F6" s="16">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2166,14 +2166,14 @@
       <c r="B7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="42">
         <v>5</v>
       </c>
       <c r="D7" s="22">
         <f>C7*Detalle!G39/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="42"/>
       <c r="F7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2183,14 +2183,14 @@
       <c r="B8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="42">
         <v>5</v>
       </c>
       <c r="D8" s="22">
         <f>C8*Detalle!I39/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="42"/>
       <c r="F8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2200,14 +2200,14 @@
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="42">
         <v>5</v>
       </c>
       <c r="D9" s="22">
         <f>C9*Detalle!K39/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="26"/>
+      <c r="E9" s="42"/>
       <c r="F9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2217,14 +2217,14 @@
       <c r="B10" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="42">
         <v>5</v>
       </c>
       <c r="D10" s="22">
         <f>C10*Detalle!M39/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="42"/>
       <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2234,14 +2234,14 @@
       <c r="B11" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="42">
         <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>C11*Detalle!O39/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="42"/>
       <c r="F11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2251,14 +2251,14 @@
       <c r="B12" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="42">
         <v>5</v>
       </c>
       <c r="D12" s="22">
         <f>C12*Detalle!Q39/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="26"/>
+      <c r="E12" s="42"/>
       <c r="F12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2268,14 +2268,14 @@
       <c r="B13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="42">
         <v>5</v>
       </c>
       <c r="D13" s="22">
         <f>C13*Detalle!S39/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="26"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2285,14 +2285,14 @@
       <c r="B14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="42">
         <v>5</v>
       </c>
       <c r="D14" s="22">
         <f>C14*Detalle!U39/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="42"/>
       <c r="F14" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2302,14 +2302,14 @@
       <c r="B15" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="42">
         <v>5</v>
       </c>
       <c r="D15" s="22">
         <f>C15*Detalle!W39/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="26"/>
+      <c r="E15" s="42"/>
       <c r="F15" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2319,14 +2319,14 @@
       <c r="B16" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="42">
         <v>5</v>
       </c>
       <c r="D16" s="22">
         <f>C16*Detalle!Y39/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="26"/>
+      <c r="E16" s="42"/>
       <c r="F16" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2336,14 +2336,14 @@
       <c r="B17" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="42">
         <v>5</v>
       </c>
       <c r="D17" s="22">
         <f>C17*Detalle!AA39/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="26"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2353,35 +2353,35 @@
       <c r="B18" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="43">
         <v>5</v>
       </c>
       <c r="D18" s="23">
         <f>C18*Detalle!AC39/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="27"/>
+      <c r="E18" s="43"/>
       <c r="F18" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="43" t="str">
+      <c r="B19" s="33" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A05 en GitHub.</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2458,82 +2458,82 @@
     </row>
     <row r="2" spans="1:30" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="37" t="str">
+      <c r="C2" s="36" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="41" t="str">
+      <c r="D2" s="37"/>
+      <c r="E2" s="40" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="41" t="str">
+      <c r="F2" s="41"/>
+      <c r="G2" s="40" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="37" t="str">
+      <c r="H2" s="41"/>
+      <c r="I2" s="36" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="37" t="str">
+      <c r="J2" s="37"/>
+      <c r="K2" s="36" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="L2" s="38"/>
-      <c r="M2" s="37" t="str">
+      <c r="L2" s="37"/>
+      <c r="M2" s="36" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="N2" s="38"/>
-      <c r="O2" s="37" t="str">
+      <c r="N2" s="37"/>
+      <c r="O2" s="36" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="37" t="str">
+      <c r="P2" s="37"/>
+      <c r="Q2" s="36" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="R2" s="38"/>
-      <c r="S2" s="37" t="str">
+      <c r="R2" s="37"/>
+      <c r="S2" s="36" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="T2" s="38"/>
-      <c r="U2" s="37" t="str">
+      <c r="T2" s="37"/>
+      <c r="U2" s="36" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="V2" s="38"/>
-      <c r="W2" s="37" t="str">
+      <c r="V2" s="37"/>
+      <c r="W2" s="36" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="37" t="str">
+      <c r="X2" s="37"/>
+      <c r="Y2" s="36" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="37" t="str">
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="36" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="37" t="str">
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="36" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AD2" s="38"/>
+      <c r="AD2" s="37"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B3" s="36"/>
+      <c r="B3" s="35"/>
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -2623,1258 +2623,1258 @@
       <c r="B4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="28">
-        <v>0</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="28">
-        <v>0</v>
-      </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="28">
-        <v>0</v>
-      </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="28">
-        <v>0</v>
-      </c>
-      <c r="J4" s="29"/>
-      <c r="K4" s="28">
-        <v>0</v>
-      </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="28">
-        <v>0</v>
-      </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="28">
-        <v>0</v>
-      </c>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="28">
-        <v>0</v>
-      </c>
-      <c r="R4" s="29"/>
-      <c r="S4" s="28">
-        <v>0</v>
-      </c>
-      <c r="T4" s="29"/>
-      <c r="U4" s="28">
-        <v>0</v>
-      </c>
-      <c r="V4" s="29"/>
-      <c r="W4" s="28">
-        <v>0</v>
-      </c>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="28">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="28">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="28">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="29"/>
+      <c r="C4" s="26">
+        <v>0</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="26">
+        <v>0</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="26">
+        <v>0</v>
+      </c>
+      <c r="H4" s="27"/>
+      <c r="I4" s="26">
+        <v>0</v>
+      </c>
+      <c r="J4" s="27"/>
+      <c r="K4" s="26">
+        <v>0</v>
+      </c>
+      <c r="L4" s="27"/>
+      <c r="M4" s="26">
+        <v>0</v>
+      </c>
+      <c r="N4" s="27"/>
+      <c r="O4" s="26">
+        <v>0</v>
+      </c>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="26">
+        <v>0</v>
+      </c>
+      <c r="R4" s="27"/>
+      <c r="S4" s="26">
+        <v>0</v>
+      </c>
+      <c r="T4" s="27"/>
+      <c r="U4" s="26">
+        <v>0</v>
+      </c>
+      <c r="V4" s="27"/>
+      <c r="W4" s="26">
+        <v>0</v>
+      </c>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="26">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="26">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="26">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="27"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="29"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="26"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="26"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="26"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="26"/>
+      <c r="AD5" s="27"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="29"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="26"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="26"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="26"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="26"/>
+      <c r="AD6" s="27"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="29"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="26"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="27"/>
+      <c r="AC7" s="26"/>
+      <c r="AD7" s="27"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="29"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="27"/>
+      <c r="AC8" s="26"/>
+      <c r="AD8" s="27"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="29"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="27"/>
     </row>
     <row r="10" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="28"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="29"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="26"/>
+      <c r="AD10" s="27"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B11" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="28"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="28"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="28"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="29"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="26"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="26"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="26"/>
+      <c r="AD11" s="27"/>
     </row>
     <row r="12" spans="1:30" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="28"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="29"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="26"/>
+      <c r="AD12" s="27"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="29"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="26"/>
+      <c r="AD13" s="27"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B14" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="28"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="28"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="28"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="29"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="26"/>
+      <c r="AD14" s="27"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="29"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="26"/>
+      <c r="AD15" s="27"/>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="28"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="29"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="26"/>
+      <c r="AD16" s="27"/>
     </row>
     <row r="17" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B17" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="28"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="28"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="29"/>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="29"/>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="29"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="26"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="26"/>
+      <c r="AB17" s="27"/>
+      <c r="AC17" s="26"/>
+      <c r="AD17" s="27"/>
     </row>
     <row r="18" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B18" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="28"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="29"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="29"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="27"/>
+      <c r="AC18" s="26"/>
+      <c r="AD18" s="27"/>
     </row>
     <row r="19" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="29"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="29"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="29"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="26"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="26"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="26"/>
+      <c r="AB19" s="27"/>
+      <c r="AC19" s="26"/>
+      <c r="AD19" s="27"/>
     </row>
     <row r="20" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B20" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="29"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="27"/>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="26"/>
+      <c r="AB20" s="27"/>
+      <c r="AC20" s="26"/>
+      <c r="AD20" s="27"/>
     </row>
     <row r="21" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="28"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="28"/>
-      <c r="X21" s="29"/>
-      <c r="Y21" s="28"/>
-      <c r="Z21" s="29"/>
-      <c r="AA21" s="28"/>
-      <c r="AB21" s="29"/>
-      <c r="AC21" s="28"/>
-      <c r="AD21" s="29"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="26"/>
+      <c r="V21" s="27"/>
+      <c r="W21" s="26"/>
+      <c r="X21" s="27"/>
+      <c r="Y21" s="26"/>
+      <c r="Z21" s="27"/>
+      <c r="AA21" s="26"/>
+      <c r="AB21" s="27"/>
+      <c r="AC21" s="26"/>
+      <c r="AD21" s="27"/>
     </row>
     <row r="22" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="28"/>
-      <c r="X22" s="29"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="29"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="26"/>
+      <c r="Z22" s="27"/>
+      <c r="AA22" s="26"/>
+      <c r="AB22" s="27"/>
+      <c r="AC22" s="26"/>
+      <c r="AD22" s="27"/>
     </row>
     <row r="23" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="29"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="26"/>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="26"/>
+      <c r="Z23" s="27"/>
+      <c r="AA23" s="26"/>
+      <c r="AB23" s="27"/>
+      <c r="AC23" s="26"/>
+      <c r="AD23" s="27"/>
     </row>
     <row r="24" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B24" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="28"/>
-      <c r="X24" s="29"/>
-      <c r="Y24" s="28"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="28"/>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="29"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="26"/>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="26"/>
+      <c r="Z24" s="27"/>
+      <c r="AA24" s="26"/>
+      <c r="AB24" s="27"/>
+      <c r="AC24" s="26"/>
+      <c r="AD24" s="27"/>
     </row>
     <row r="25" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B25" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="29"/>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="29"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="29"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="29"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="27"/>
+      <c r="W25" s="26"/>
+      <c r="X25" s="27"/>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="27"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="27"/>
+      <c r="AC25" s="26"/>
+      <c r="AD25" s="27"/>
     </row>
     <row r="26" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B26" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="28"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="29"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="26"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="26"/>
+      <c r="AB26" s="27"/>
+      <c r="AC26" s="26"/>
+      <c r="AD26" s="27"/>
     </row>
     <row r="27" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B27" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="28"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="28"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="29"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="26"/>
+      <c r="AD27" s="27"/>
     </row>
     <row r="28" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B28" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="29"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="29"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="26"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="26"/>
+      <c r="AD28" s="27"/>
     </row>
     <row r="29" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B29" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="29"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="26"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="26"/>
+      <c r="V29" s="27"/>
+      <c r="W29" s="26"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="26"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="26"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="26"/>
+      <c r="AD29" s="27"/>
     </row>
     <row r="30" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B30" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="28"/>
-      <c r="V30" s="29"/>
-      <c r="W30" s="28"/>
-      <c r="X30" s="29"/>
-      <c r="Y30" s="28"/>
-      <c r="Z30" s="29"/>
-      <c r="AA30" s="28"/>
-      <c r="AB30" s="29"/>
-      <c r="AC30" s="28"/>
-      <c r="AD30" s="29"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="27"/>
+      <c r="W30" s="26"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="26"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="26"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="26"/>
+      <c r="AD30" s="27"/>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B31" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="28"/>
-      <c r="V31" s="29"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="29"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="29"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="29"/>
-      <c r="AC31" s="28"/>
-      <c r="AD31" s="29"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="27"/>
+      <c r="W31" s="26"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="26"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="26"/>
+      <c r="AB31" s="27"/>
+      <c r="AC31" s="26"/>
+      <c r="AD31" s="27"/>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.45">
       <c r="B32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="28"/>
-      <c r="AD32" s="29"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="27"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="26"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="26"/>
+      <c r="AB32" s="27"/>
+      <c r="AC32" s="26"/>
+      <c r="AD32" s="27"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B33" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="29"/>
-      <c r="Y33" s="28"/>
-      <c r="Z33" s="29"/>
-      <c r="AA33" s="28"/>
-      <c r="AB33" s="29"/>
-      <c r="AC33" s="28"/>
-      <c r="AD33" s="29"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="27"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="27"/>
+      <c r="Y33" s="26"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="26"/>
+      <c r="AB33" s="27"/>
+      <c r="AC33" s="26"/>
+      <c r="AD33" s="27"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B34" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="29"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="29"/>
-      <c r="Y34" s="28"/>
-      <c r="Z34" s="29"/>
-      <c r="AA34" s="28"/>
-      <c r="AB34" s="29"/>
-      <c r="AC34" s="28"/>
-      <c r="AD34" s="29"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="27"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="27"/>
+      <c r="W34" s="26"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="26"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="26"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="26"/>
+      <c r="AD34" s="27"/>
     </row>
     <row r="35" spans="1:30" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B35" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="28"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="29"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="29"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="29"/>
-      <c r="AC35" s="28"/>
-      <c r="AD35" s="29"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="26"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="26"/>
+      <c r="V35" s="27"/>
+      <c r="W35" s="26"/>
+      <c r="X35" s="27"/>
+      <c r="Y35" s="26"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="26"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="26"/>
+      <c r="AD35" s="27"/>
     </row>
     <row r="36" spans="1:30" ht="138.4" x14ac:dyDescent="0.45">
       <c r="B36" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="29"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="29"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="29"/>
-      <c r="AC36" s="28"/>
-      <c r="AD36" s="29"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="27"/>
+      <c r="W36" s="26"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="26"/>
+      <c r="Z36" s="27"/>
+      <c r="AA36" s="26"/>
+      <c r="AB36" s="27"/>
+      <c r="AC36" s="26"/>
+      <c r="AD36" s="27"/>
     </row>
     <row r="37" spans="1:30" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B37" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="29"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="26"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="26"/>
+      <c r="V37" s="27"/>
+      <c r="W37" s="26"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="26"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="26"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="26"/>
+      <c r="AD37" s="27"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B38" s="30"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="32"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="32"/>
-      <c r="S38" s="31"/>
-      <c r="T38" s="32"/>
-      <c r="U38" s="31"/>
-      <c r="V38" s="32"/>
-      <c r="W38" s="31"/>
-      <c r="X38" s="32"/>
-      <c r="Y38" s="31"/>
-      <c r="Z38" s="32"/>
-      <c r="AA38" s="31"/>
-      <c r="AB38" s="32"/>
-      <c r="AC38" s="31"/>
-      <c r="AD38" s="32"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="29"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="29"/>
+      <c r="Z38" s="30"/>
+      <c r="AA38" s="29"/>
+      <c r="AB38" s="30"/>
+      <c r="AC38" s="29"/>
+      <c r="AD38" s="30"/>
     </row>
     <row r="39" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1"/>
-      <c r="B39" s="33" t="s">
+      <c r="B39" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="39">
+      <c r="C39" s="38">
         <f>AVERAGE(C4:C38)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="40"/>
-      <c r="E39" s="39">
+      <c r="D39" s="39"/>
+      <c r="E39" s="38">
         <f>AVERAGE(E4:E38)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="40"/>
-      <c r="G39" s="39">
+      <c r="F39" s="39"/>
+      <c r="G39" s="38">
         <f>AVERAGE(G4:G38)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39">
+      <c r="H39" s="38"/>
+      <c r="I39" s="38">
         <f>AVERAGE(I4:I38)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="40"/>
-      <c r="K39" s="39">
+      <c r="J39" s="39"/>
+      <c r="K39" s="38">
         <f>AVERAGE(K4:K38)</f>
         <v>0</v>
       </c>
-      <c r="L39" s="40"/>
-      <c r="M39" s="39">
+      <c r="L39" s="39"/>
+      <c r="M39" s="38">
         <f>AVERAGE(M4:M38)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="40"/>
-      <c r="O39" s="39">
+      <c r="N39" s="39"/>
+      <c r="O39" s="38">
         <f>AVERAGE(O4:O38)</f>
         <v>0</v>
       </c>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="39">
+      <c r="P39" s="39"/>
+      <c r="Q39" s="38">
         <f>AVERAGE(Q4:Q38)</f>
         <v>0</v>
       </c>
-      <c r="R39" s="40"/>
-      <c r="S39" s="39">
+      <c r="R39" s="39"/>
+      <c r="S39" s="38">
         <f>AVERAGE(S4:S38)</f>
         <v>0</v>
       </c>
-      <c r="T39" s="40"/>
-      <c r="U39" s="39">
+      <c r="T39" s="39"/>
+      <c r="U39" s="38">
         <f>AVERAGE(U4:U38)</f>
         <v>0</v>
       </c>
-      <c r="V39" s="40"/>
-      <c r="W39" s="39">
+      <c r="V39" s="39"/>
+      <c r="W39" s="38">
         <f>AVERAGE(W4:W38)</f>
         <v>0</v>
       </c>
-      <c r="X39" s="40"/>
-      <c r="Y39" s="39">
+      <c r="X39" s="39"/>
+      <c r="Y39" s="38">
         <f>AVERAGE(Y4:Y38)</f>
         <v>0</v>
       </c>
-      <c r="Z39" s="40"/>
-      <c r="AA39" s="39">
+      <c r="Z39" s="39"/>
+      <c r="AA39" s="38">
         <f>AVERAGE(AA4:AA38)</f>
         <v>0</v>
       </c>
-      <c r="AB39" s="40"/>
-      <c r="AC39" s="39">
+      <c r="AB39" s="39"/>
+      <c r="AC39" s="38">
         <f>AVERAGE(AC4:AC38)</f>
         <v>0</v>
       </c>
-      <c r="AD39" s="40"/>
+      <c r="AD39" s="39"/>
     </row>
     <row r="40" spans="1:30" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B40" s="3"/>

--- a/activity/M01A05/M01A05_HECRASSample.xlsx
+++ b/activity/M01A05/M01A05_HECRASSample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29309"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF17143-EFCE-4144-9BCC-A4CBA0CB7AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E03FD00-11B7-48D3-A97C-FA7831377D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>Modelo RAS Mapper. Red con eje valle proyecto (incluir en reporte:  planta de cada capa, líneas con direcciones vectoriales y tabla de atributos)</t>
   </si>
   <si>
-    <t>Cargar en la carpeta /file/hec del repositorio de datos, los archivos comprimidos del modelo RAS como HECRAS_Natural_v0.zip y HECRAS_Anthropic_v0.zip.</t>
-  </si>
-  <si>
     <t>Banks (en el modelo de muestreo que incluye el valle suavizado, las líneas de banca paralelas solo al eje de los tramos de nuevo valle, deben ser localizadas a 150m a cada lado, esto permitirá evaluar los cortes y rellenos a analizar en entregas posteriores.)</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto. (reporte único en Adobe Acrobat que integre todos los modelos y reportes, utilizar separadores con títulos que indiquen el contenido de cada modelo).</t>
+  </si>
+  <si>
+    <t>Cargar en la carpeta /file/hec del repositorio de datos, los archivos comprimidos del modelo RAS como HECRAS_v0.zip.</t>
   </si>
 </sst>
 </file>
@@ -636,28 +636,28 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -666,11 +666,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2096,20 +2096,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
@@ -2132,14 +2132,14 @@
       <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="32">
         <v>5</v>
       </c>
       <c r="D5" s="22">
         <f>C5*Detalle!C39/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="42"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="16">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2149,14 +2149,14 @@
       <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="32">
         <v>5</v>
       </c>
       <c r="D6" s="22">
         <f>C6*Detalle!E39/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="42"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="16">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2166,14 +2166,14 @@
       <c r="B7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="32">
         <v>5</v>
       </c>
       <c r="D7" s="22">
         <f>C7*Detalle!G39/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="42"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2183,14 +2183,14 @@
       <c r="B8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="32">
         <v>5</v>
       </c>
       <c r="D8" s="22">
         <f>C8*Detalle!I39/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="42"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2200,14 +2200,14 @@
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="32">
         <v>5</v>
       </c>
       <c r="D9" s="22">
         <f>C9*Detalle!K39/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="42"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2217,14 +2217,14 @@
       <c r="B10" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="32">
         <v>5</v>
       </c>
       <c r="D10" s="22">
         <f>C10*Detalle!M39/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="42"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2234,14 +2234,14 @@
       <c r="B11" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="32">
         <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>C11*Detalle!O39/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="42"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2251,14 +2251,14 @@
       <c r="B12" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="32">
         <v>5</v>
       </c>
       <c r="D12" s="22">
         <f>C12*Detalle!Q39/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="42"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2268,14 +2268,14 @@
       <c r="B13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="32">
         <v>5</v>
       </c>
       <c r="D13" s="22">
         <f>C13*Detalle!S39/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="42"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2285,14 +2285,14 @@
       <c r="B14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="32">
         <v>5</v>
       </c>
       <c r="D14" s="22">
         <f>C14*Detalle!U39/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="42"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2302,14 +2302,14 @@
       <c r="B15" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="32">
         <v>5</v>
       </c>
       <c r="D15" s="22">
         <f>C15*Detalle!W39/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="42"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2319,14 +2319,14 @@
       <c r="B16" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="32">
         <v>5</v>
       </c>
       <c r="D16" s="22">
         <f>C16*Detalle!Y39/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="42"/>
+      <c r="E16" s="32"/>
       <c r="F16" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2336,14 +2336,14 @@
       <c r="B17" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="32">
         <v>5</v>
       </c>
       <c r="D17" s="22">
         <f>C17*Detalle!AA39/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="42"/>
+      <c r="E17" s="32"/>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2353,35 +2353,35 @@
       <c r="B18" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="33">
         <v>5</v>
       </c>
       <c r="D18" s="23">
         <f>C18*Detalle!AC39/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="43"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="33" t="str">
+      <c r="B19" s="35" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A05 en GitHub.</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2458,14 +2458,14 @@
     </row>
     <row r="2" spans="1:30" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="36" t="str">
+      <c r="C2" s="38" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="37"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="40" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
@@ -2476,64 +2476,64 @@
         <v>Grupo 3</v>
       </c>
       <c r="H2" s="41"/>
-      <c r="I2" s="36" t="str">
+      <c r="I2" s="38" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="36" t="str">
+      <c r="J2" s="39"/>
+      <c r="K2" s="38" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="L2" s="37"/>
-      <c r="M2" s="36" t="str">
+      <c r="L2" s="39"/>
+      <c r="M2" s="38" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="N2" s="37"/>
-      <c r="O2" s="36" t="str">
+      <c r="N2" s="39"/>
+      <c r="O2" s="38" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="36" t="str">
+      <c r="P2" s="39"/>
+      <c r="Q2" s="38" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="R2" s="37"/>
-      <c r="S2" s="36" t="str">
+      <c r="R2" s="39"/>
+      <c r="S2" s="38" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="T2" s="37"/>
-      <c r="U2" s="36" t="str">
+      <c r="T2" s="39"/>
+      <c r="U2" s="38" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="V2" s="37"/>
-      <c r="W2" s="36" t="str">
+      <c r="V2" s="39"/>
+      <c r="W2" s="38" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="36" t="str">
+      <c r="X2" s="39"/>
+      <c r="Y2" s="38" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="36" t="str">
+      <c r="Z2" s="39"/>
+      <c r="AA2" s="38" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="36" t="str">
+      <c r="AB2" s="39"/>
+      <c r="AC2" s="38" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AD2" s="37"/>
+      <c r="AD2" s="39"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B3" s="35"/>
+      <c r="B3" s="43"/>
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="12" spans="1:30" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="27"/>
@@ -3670,9 +3670,9 @@
       <c r="AC34" s="26"/>
       <c r="AD34" s="27"/>
     </row>
-    <row r="35" spans="1:30" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B35" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="27"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="36" spans="1:30" ht="138.4" x14ac:dyDescent="0.45">
       <c r="B36" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="27"/>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="37" spans="1:30" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B37" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="27"/>
@@ -3805,76 +3805,76 @@
       <c r="B39" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="36">
         <f>AVERAGE(C4:C38)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="38">
+      <c r="D39" s="37"/>
+      <c r="E39" s="36">
         <f>AVERAGE(E4:E38)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="39"/>
-      <c r="G39" s="38">
+      <c r="F39" s="37"/>
+      <c r="G39" s="36">
         <f>AVERAGE(G4:G38)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38">
+      <c r="H39" s="36"/>
+      <c r="I39" s="36">
         <f>AVERAGE(I4:I38)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="39"/>
-      <c r="K39" s="38">
+      <c r="J39" s="37"/>
+      <c r="K39" s="36">
         <f>AVERAGE(K4:K38)</f>
         <v>0</v>
       </c>
-      <c r="L39" s="39"/>
-      <c r="M39" s="38">
+      <c r="L39" s="37"/>
+      <c r="M39" s="36">
         <f>AVERAGE(M4:M38)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="39"/>
-      <c r="O39" s="38">
+      <c r="N39" s="37"/>
+      <c r="O39" s="36">
         <f>AVERAGE(O4:O38)</f>
         <v>0</v>
       </c>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="38">
+      <c r="P39" s="37"/>
+      <c r="Q39" s="36">
         <f>AVERAGE(Q4:Q38)</f>
         <v>0</v>
       </c>
-      <c r="R39" s="39"/>
-      <c r="S39" s="38">
+      <c r="R39" s="37"/>
+      <c r="S39" s="36">
         <f>AVERAGE(S4:S38)</f>
         <v>0</v>
       </c>
-      <c r="T39" s="39"/>
-      <c r="U39" s="38">
+      <c r="T39" s="37"/>
+      <c r="U39" s="36">
         <f>AVERAGE(U4:U38)</f>
         <v>0</v>
       </c>
-      <c r="V39" s="39"/>
-      <c r="W39" s="38">
+      <c r="V39" s="37"/>
+      <c r="W39" s="36">
         <f>AVERAGE(W4:W38)</f>
         <v>0</v>
       </c>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="38">
+      <c r="X39" s="37"/>
+      <c r="Y39" s="36">
         <f>AVERAGE(Y4:Y38)</f>
         <v>0</v>
       </c>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="38">
+      <c r="Z39" s="37"/>
+      <c r="AA39" s="36">
         <f>AVERAGE(AA4:AA38)</f>
         <v>0</v>
       </c>
-      <c r="AB39" s="39"/>
-      <c r="AC39" s="38">
+      <c r="AB39" s="37"/>
+      <c r="AC39" s="36">
         <f>AVERAGE(AC4:AC38)</f>
         <v>0</v>
       </c>
-      <c r="AD39" s="39"/>
+      <c r="AD39" s="37"/>
     </row>
     <row r="40" spans="1:30" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B40" s="3"/>
@@ -4994,19 +4994,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="AA39:AB39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="Y39:Z39"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AC2:AD2"/>
     <mergeCell ref="AC39:AD39"/>
@@ -5023,6 +5010,19 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="AA39:AB39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="Y39:Z39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
